--- a/public/vorlagen/vorlage-zeitreihe.xlsx
+++ b/public/vorlagen/vorlage-zeitreihe.xlsx
@@ -544,6 +544,9 @@
       <c r="B13">
         <v>10475</v>
       </c>
+      <c r="C13">
+        <v>3784</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
